--- a/Input List/Full Band/Split Map.xlsx
+++ b/Input List/Full Band/Split Map.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\TechnicalDocumentation\Input List\Full Band\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\TechnicalDocumentation\Input List\Full Band\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F651A74-CC90-41CB-9465-61EE0D9F570B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9150DACB-539E-4F87-B85C-7C463A74F560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{976BA9A3-41FE-45E5-BC0B-B40312D9AF21}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{976BA9A3-41FE-45E5-BC0B-B40312D9AF21}"/>
   </bookViews>
   <sheets>
     <sheet name="Split Map" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>Top</t>
   </si>
@@ -63,30 +62,13 @@
     <t>Crowd Right</t>
   </si>
   <si>
-    <t>Vocals 1 DSR</t>
-  </si>
-  <si>
-    <t>Vocals 2 DCR</t>
-  </si>
-  <si>
     <t>Vocals 5 USC</t>
   </si>
   <si>
-    <t>Keyboard DSL</t>
-  </si>
-  <si>
     <t>SL Overhd USC</t>
   </si>
   <si>
     <t>SR Overhd USC</t>
-  </si>
-  <si>
-    <t>Bass
-DSR</t>
-  </si>
-  <si>
-    <t>Piano
-DSL</t>
   </si>
   <si>
     <t>Kick
@@ -117,25 +99,10 @@
 USC</t>
   </si>
   <si>
-    <t>Guitar 1 (A) DCR</t>
-  </si>
-  <si>
-    <t>Guitar 2 (E) DCL</t>
-  </si>
-  <si>
-    <t>Guitar 3 (E) DSL</t>
-  </si>
-  <si>
-    <t>Guitar 4 (A) DSL</t>
-  </si>
-  <si>
     <t>|--- Bass ---|</t>
   </si>
   <si>
     <t>| Talkback |</t>
-  </si>
-  <si>
-    <t>|-------------------------------------- Vocals -------------------------------------|</t>
   </si>
   <si>
     <t>|---------------------------- Guitars --------------------------|</t>
@@ -158,22 +125,61 @@
 IEM</t>
   </si>
   <si>
-    <t>|----------------------------- In-Ear Monitors --------------------------------|</t>
-  </si>
-  <si>
     <t>|--------------------------------------------------------------- Drums -----------------------------------------------------------------</t>
-  </si>
-  <si>
-    <t>Vocals 3
-DCL</t>
-  </si>
-  <si>
-    <t>Vocals 4
-DSL</t>
   </si>
   <si>
     <t>Billy
 IEM</t>
+  </si>
+  <si>
+    <t>Vocals 6 DSR</t>
+  </si>
+  <si>
+    <t>Vocals 1 USR</t>
+  </si>
+  <si>
+    <t>Vocals 2 DSC</t>
+  </si>
+  <si>
+    <t>Vocals 3
+DSL</t>
+  </si>
+  <si>
+    <t>Vocals 4
+USL</t>
+  </si>
+  <si>
+    <t>Piano
+USL</t>
+  </si>
+  <si>
+    <t>Keyboard USL</t>
+  </si>
+  <si>
+    <t>Guitar 1 (A) DSC</t>
+  </si>
+  <si>
+    <t>Guitar 2 (E) DSL</t>
+  </si>
+  <si>
+    <t>Guitar 3 (E) DSR</t>
+  </si>
+  <si>
+    <t>Bass
+USR</t>
+  </si>
+  <si>
+    <t>???
+IEM</t>
+  </si>
+  <si>
+    <t>|---------------------------------------------- In-Ear Monitors -------------------------------------------------|</t>
+  </si>
+  <si>
+    <t>|---------------------------------------------- Vocals ---------------------------------------------|</t>
+  </si>
+  <si>
+    <t>Guitar 4 (A) USL</t>
   </si>
 </sst>
 </file>
@@ -251,7 +257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,6 +321,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -409,9 +421,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -427,6 +436,45 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -436,48 +484,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,300 +827,303 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="J1" s="12" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="16">
         <v>2</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="16">
         <v>3</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="16">
         <v>4</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="17">
         <v>5</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="17">
         <v>6</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="17">
         <v>7</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="17">
         <v>8</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2" s="21">
         <v>9</v>
       </c>
-      <c r="K2" s="26">
+      <c r="K2" s="21">
         <v>10</v>
       </c>
-      <c r="L2" s="26">
+      <c r="L2" s="21">
         <v>11</v>
       </c>
-      <c r="M2" s="26">
+      <c r="M2" s="21">
         <v>12</v>
       </c>
-      <c r="N2" s="23">
+      <c r="N2" s="18">
         <v>13</v>
       </c>
-      <c r="O2" s="23">
+      <c r="O2" s="18">
         <v>14</v>
       </c>
-      <c r="P2" s="23">
+      <c r="P2" s="18">
         <v>15</v>
       </c>
-      <c r="Q2" s="23">
+      <c r="Q2" s="18">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="45" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="17" t="s">
+      <c r="P3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8" t="str">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7" t="str">
         <f>"---------------|"</f>
         <v>---------------|</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="8"/>
+      <c r="K4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="J5" s="12" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="J5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="20">
         <v>17</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="20">
         <v>18</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="20">
         <v>19</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="20">
         <v>20</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="22">
         <v>21</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="22">
         <v>22</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="22">
         <v>23</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="22">
         <v>24</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="19">
         <v>25</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="19">
         <v>26</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="19">
         <v>27</v>
       </c>
-      <c r="M6" s="24">
+      <c r="M6" s="19">
         <v>28</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="19">
         <v>29</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="19">
         <v>30</v>
       </c>
-      <c r="P6" s="24">
+      <c r="P6" s="19">
         <v>31</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="Q6" s="19">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="17" t="s">
+      <c r="L7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="M7" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="N7" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="20" t="s">
+      <c r="P7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="Q7" s="20" t="s">
+      <c r="Q7" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9" t="s">
-        <v>27</v>
+      <c r="A8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1126,27 +1142,27 @@
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="6"/>
+      <c r="A10" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:17" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="1"/>
     </row>
   </sheetData>
